--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -74,6 +74,38 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pankaj Duggal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Principal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Innocent Hearts School</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9216194630</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19T05:40:13+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -45,12 +45,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balwinder kaur</t>
+          <t xml:space="preserve">Pankaj Duggal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -60,49 +60,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pioneer international public school</t>
+          <t xml:space="preserve">Innocent Hearts School</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9216194613</t>
+          <t xml:space="preserve">9216194630</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T04:20:24+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pankaj Duggal</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Principal</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Innocent Hearts School</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9216194630</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-19T05:40:13+00:00</t>
+          <t xml:space="preserve">2026-10-19T06:08:49+00:00</t>
         </is>
       </c>
     </row>
